--- a/foxconn/dist/20261025_鴻海模型_v0.2.xlsx
+++ b/foxconn/dist/20261025_鴻海模型_v0.2.xlsx
@@ -6272,7 +6272,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6490,7 +6490,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6611,7 +6611,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6732,7 +6732,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6853,7 +6853,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6974,7 +6974,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
